--- a/CONTROLGARAJE.xlsx
+++ b/CONTROLGARAJE.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="191">
   <si>
     <t>PLACA</t>
   </si>
@@ -633,6 +633,9 @@
   </si>
   <si>
     <t>SE RETIRA DEBE LLAVE</t>
+  </si>
+  <si>
+    <t>NO PAGO MOTOS DESDE ENE 300 BS, TOTAL 900</t>
   </si>
 </sst>
 </file>
@@ -1155,11 +1158,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:G50" totalsRowShown="0">
-  <autoFilter ref="A1:G50">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:G60" totalsRowShown="0">
+  <autoFilter ref="A1:G60">
     <filterColumn colId="0">
       <filters>
-        <filter val="2358NDY"/>
+        <filter val="1758GXK"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -1656,7 +1659,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
@@ -1793,7 +1796,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="41" t="s">
         <v>1</v>
       </c>
@@ -1816,7 +1819,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="41" t="s">
         <v>1</v>
       </c>
@@ -1836,7 +1839,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="41" t="s">
         <v>1</v>
       </c>
@@ -1856,7 +1859,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="41" t="s">
         <v>1</v>
       </c>
@@ -1876,7 +1879,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="41" t="s">
         <v>1</v>
       </c>
@@ -1899,7 +1902,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>126</v>
       </c>
@@ -1962,7 +1965,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="41" t="s">
         <v>1</v>
       </c>
@@ -1982,7 +1985,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>126</v>
       </c>
@@ -2042,7 +2045,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>126</v>
       </c>
@@ -2125,7 +2128,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>126</v>
       </c>
@@ -2188,7 +2191,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="41" t="s">
         <v>1</v>
       </c>
@@ -2251,7 +2254,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>126</v>
       </c>
@@ -2271,7 +2274,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>126</v>
       </c>
@@ -2331,7 +2334,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="41" t="s">
         <v>1</v>
       </c>
@@ -2351,7 +2354,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="41" t="s">
         <v>1</v>
       </c>
@@ -2374,7 +2377,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>126</v>
       </c>
@@ -2454,7 +2457,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>126</v>
       </c>
@@ -2537,7 +2540,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>126</v>
       </c>
@@ -2577,7 +2580,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>126</v>
       </c>
@@ -2702,6 +2705,210 @@
       <c r="G50">
         <v>2026</v>
       </c>
+    </row>
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>126</v>
+      </c>
+      <c r="B51" s="41">
+        <v>46086</v>
+      </c>
+      <c r="C51" s="54">
+        <v>150</v>
+      </c>
+      <c r="D51" s="1">
+        <v>0</v>
+      </c>
+      <c r="E51" t="s">
+        <v>58</v>
+      </c>
+      <c r="G51">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>162</v>
+      </c>
+      <c r="B52" s="41">
+        <v>46099</v>
+      </c>
+      <c r="C52" s="54">
+        <v>150</v>
+      </c>
+      <c r="D52" s="1">
+        <v>0</v>
+      </c>
+      <c r="E52" t="s">
+        <v>58</v>
+      </c>
+      <c r="G52">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>173</v>
+      </c>
+      <c r="B53" s="41">
+        <v>46066</v>
+      </c>
+      <c r="C53" s="54">
+        <v>60</v>
+      </c>
+      <c r="D53" s="1">
+        <v>0</v>
+      </c>
+      <c r="E53" t="s">
+        <v>52</v>
+      </c>
+      <c r="G53">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>173</v>
+      </c>
+      <c r="B54" s="41">
+        <v>46095</v>
+      </c>
+      <c r="C54" s="54">
+        <v>60</v>
+      </c>
+      <c r="D54" s="1">
+        <v>0</v>
+      </c>
+      <c r="E54" t="s">
+        <v>58</v>
+      </c>
+      <c r="G54">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="B55" s="41">
+        <v>46001</v>
+      </c>
+      <c r="C55" s="54">
+        <v>0</v>
+      </c>
+      <c r="D55" s="1">
+        <v>150</v>
+      </c>
+      <c r="E55" t="s">
+        <v>83</v>
+      </c>
+      <c r="F55" t="s">
+        <v>71</v>
+      </c>
+      <c r="G55">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="B56" s="41">
+        <v>46032</v>
+      </c>
+      <c r="C56" s="54">
+        <f>DETALLE!I83</f>
+        <v>0</v>
+      </c>
+      <c r="D56" s="1">
+        <v>300</v>
+      </c>
+      <c r="E56" t="s">
+        <v>53</v>
+      </c>
+      <c r="F56" t="s">
+        <v>71</v>
+      </c>
+      <c r="G56">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="B57" s="41">
+        <v>46063</v>
+      </c>
+      <c r="C57" s="54">
+        <f>DETALLE!I84</f>
+        <v>0</v>
+      </c>
+      <c r="D57" s="1">
+        <v>450</v>
+      </c>
+      <c r="E57" t="s">
+        <v>52</v>
+      </c>
+      <c r="F57" t="s">
+        <v>71</v>
+      </c>
+      <c r="G57">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="B58" s="41">
+        <v>42439</v>
+      </c>
+      <c r="C58" s="54">
+        <f>DETALLE!I85</f>
+        <v>0</v>
+      </c>
+      <c r="D58" s="1">
+        <v>500</v>
+      </c>
+      <c r="E58" t="s">
+        <v>58</v>
+      </c>
+      <c r="F58" t="s">
+        <v>71</v>
+      </c>
+      <c r="G58">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="B59" s="41">
+        <v>46122</v>
+      </c>
+      <c r="C59" s="54">
+        <f>DETALLE!I86</f>
+        <v>0</v>
+      </c>
+      <c r="D59" s="1">
+        <v>650</v>
+      </c>
+      <c r="E59" t="s">
+        <v>59</v>
+      </c>
+      <c r="F59" t="s">
+        <v>190</v>
+      </c>
+      <c r="G59">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="41"/>
+      <c r="B60" s="41"/>
+      <c r="C60" s="54"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/CONTROLGARAJE.xlsx
+++ b/CONTROLGARAJE.xlsx
@@ -635,7 +635,7 @@
     <t>SE RETIRA DEBE LLAVE</t>
   </si>
   <si>
-    <t>NO PAGO MOTOS DESDE ENE 300 BS, TOTAL 900</t>
+    <t>NO PAGO MOTOS DESDE ENE 200 BS, TOTAL 850</t>
   </si>
 </sst>
 </file>
@@ -1666,7 +1666,7 @@
     <col min="3" max="3" width="12" style="1" customWidth="1"/>
     <col min="4" max="4" width="15.5703125" style="1" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="20.42578125" customWidth="1"/>
+    <col min="6" max="6" width="23.42578125" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>

--- a/CONTROLGARAJE.xlsx
+++ b/CONTROLGARAJE.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="195">
   <si>
     <t>PLACA</t>
   </si>
@@ -636,6 +636,18 @@
   </si>
   <si>
     <t>NO PAGO MOTOS DESDE ENE 200 BS, TOTAL 850</t>
+  </si>
+  <si>
+    <t>DE JUNIO Y JULIO</t>
+  </si>
+  <si>
+    <t>MAS MOTOCICLETA 50+350</t>
+  </si>
+  <si>
+    <t>MAS MOTOCICLETA 150+50+400</t>
+  </si>
+  <si>
+    <t>MAS MOTOCICLETA 150+50+600</t>
   </si>
 </sst>
 </file>
@@ -1158,8 +1170,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:G60" totalsRowShown="0">
-  <autoFilter ref="A1:G60">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:G72" totalsRowShown="0">
+  <autoFilter ref="A1:G72">
     <filterColumn colId="0">
       <filters>
         <filter val="1758GXK"/>
@@ -1659,14 +1671,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="12" style="1" customWidth="1"/>
     <col min="4" max="4" width="15.5703125" style="1" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="23.42578125" customWidth="1"/>
+    <col min="6" max="6" width="34.5703125" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2905,10 +2917,264 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="41"/>
       <c r="B60" s="41"/>
       <c r="C60" s="54"/>
+    </row>
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>162</v>
+      </c>
+      <c r="B61" s="41">
+        <v>46136</v>
+      </c>
+      <c r="C61" s="54">
+        <v>150</v>
+      </c>
+      <c r="D61" s="1">
+        <v>0</v>
+      </c>
+      <c r="E61" t="s">
+        <v>59</v>
+      </c>
+      <c r="G61">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>162</v>
+      </c>
+      <c r="B62" s="41">
+        <v>46143</v>
+      </c>
+      <c r="C62" s="54">
+        <f>DETALLE!I89</f>
+        <v>0</v>
+      </c>
+      <c r="D62" s="1">
+        <v>150</v>
+      </c>
+      <c r="E62" t="s">
+        <v>60</v>
+      </c>
+      <c r="G62">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>162</v>
+      </c>
+      <c r="B63" s="41">
+        <v>46176</v>
+      </c>
+      <c r="C63" s="54">
+        <v>150</v>
+      </c>
+      <c r="D63" s="1">
+        <v>150</v>
+      </c>
+      <c r="E63" t="s">
+        <v>65</v>
+      </c>
+      <c r="G63">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>126</v>
+      </c>
+      <c r="B64" s="41">
+        <v>46118</v>
+      </c>
+      <c r="C64" s="54">
+        <v>150</v>
+      </c>
+      <c r="D64" s="1">
+        <v>0</v>
+      </c>
+      <c r="E64" t="s">
+        <v>59</v>
+      </c>
+      <c r="G64">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>126</v>
+      </c>
+      <c r="B65" s="41">
+        <v>46150</v>
+      </c>
+      <c r="C65" s="54">
+        <v>150</v>
+      </c>
+      <c r="D65" s="1">
+        <v>0</v>
+      </c>
+      <c r="E65" t="s">
+        <v>60</v>
+      </c>
+      <c r="G65">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>126</v>
+      </c>
+      <c r="B66" s="41">
+        <v>46023</v>
+      </c>
+      <c r="C66" s="54">
+        <v>150</v>
+      </c>
+      <c r="D66" s="1">
+        <v>0</v>
+      </c>
+      <c r="E66" t="s">
+        <v>65</v>
+      </c>
+      <c r="G66">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>173</v>
+      </c>
+      <c r="B67" s="41">
+        <v>46144</v>
+      </c>
+      <c r="C67" s="54">
+        <v>60</v>
+      </c>
+      <c r="D67" s="1">
+        <v>0</v>
+      </c>
+      <c r="E67" t="s">
+        <v>60</v>
+      </c>
+      <c r="G67">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>173</v>
+      </c>
+      <c r="B68" s="41">
+        <v>46177</v>
+      </c>
+      <c r="C68" s="54">
+        <v>60</v>
+      </c>
+      <c r="D68" s="1">
+        <v>0</v>
+      </c>
+      <c r="E68" t="s">
+        <v>65</v>
+      </c>
+      <c r="G68">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>173</v>
+      </c>
+      <c r="B69" s="41">
+        <v>46207</v>
+      </c>
+      <c r="C69" s="54">
+        <v>60</v>
+      </c>
+      <c r="D69" s="1">
+        <v>0</v>
+      </c>
+      <c r="E69" t="s">
+        <v>66</v>
+      </c>
+      <c r="F69" t="s">
+        <v>191</v>
+      </c>
+      <c r="G69">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="B70" s="41">
+        <v>46144</v>
+      </c>
+      <c r="C70" s="54">
+        <v>300</v>
+      </c>
+      <c r="D70" s="1">
+        <v>400</v>
+      </c>
+      <c r="E70" t="s">
+        <v>60</v>
+      </c>
+      <c r="F70" t="s">
+        <v>192</v>
+      </c>
+      <c r="G70">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="B71" s="41">
+        <v>46183</v>
+      </c>
+      <c r="C71" s="54">
+        <v>0</v>
+      </c>
+      <c r="D71" s="1">
+        <v>600</v>
+      </c>
+      <c r="E71" t="s">
+        <v>65</v>
+      </c>
+      <c r="F71" t="s">
+        <v>193</v>
+      </c>
+      <c r="G71">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="B72" s="41">
+        <v>46213</v>
+      </c>
+      <c r="C72" s="54">
+        <f>DETALLE!I99</f>
+        <v>0</v>
+      </c>
+      <c r="D72" s="1">
+        <v>800</v>
+      </c>
+      <c r="E72" t="s">
+        <v>66</v>
+      </c>
+      <c r="F72" t="s">
+        <v>194</v>
+      </c>
+      <c r="G72">
+        <v>2026</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/CONTROLGARAJE.xlsx
+++ b/CONTROLGARAJE.xlsx
@@ -14,13 +14,14 @@
   <sheets>
     <sheet name="Vehiculos" sheetId="1" r:id="rId1"/>
     <sheet name="REGISTROPAGOS" sheetId="5" r:id="rId2"/>
-    <sheet name="DETALLE" sheetId="3" r:id="rId3"/>
-    <sheet name="motos" sheetId="2" r:id="rId4"/>
-    <sheet name="Hoja1" sheetId="4" r:id="rId5"/>
-    <sheet name="Hoja4" sheetId="7" r:id="rId6"/>
+    <sheet name="REGISTROPAGOS 2025" sheetId="8" r:id="rId3"/>
+    <sheet name="DETALLE" sheetId="3" r:id="rId4"/>
+    <sheet name="motos" sheetId="2" r:id="rId5"/>
+    <sheet name="Hoja1" sheetId="4" r:id="rId6"/>
+    <sheet name="Hoja4" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="DatosExternos_1" localSheetId="5" hidden="1">Hoja4!$A$1:$Q$82</definedName>
+    <definedName name="DatosExternos_1" localSheetId="6" hidden="1">Hoja4!$A$1:$Q$82</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -63,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="195">
   <si>
     <t>PLACA</t>
   </si>
@@ -1071,7 +1072,14 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="21">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="d/m/yyyy"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -1170,20 +1178,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:G72" totalsRowShown="0">
-  <autoFilter ref="A1:G72">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="1758GXK"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:G30" totalsRowShown="0">
+  <autoFilter ref="A1:G30"/>
   <tableColumns count="7">
     <tableColumn id="1" name="PLACA"/>
-    <tableColumn id="2" name="FECHAPAGO" dataDxfId="18">
+    <tableColumn id="2" name="FECHAPAGO" dataDxfId="20">
       <calculatedColumnFormula>DETALLE!H29</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" name="MONTO" dataDxfId="17">
+    <tableColumn id="3" name="MONTO" dataDxfId="19">
       <calculatedColumnFormula>DETALLE!I29</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" name="NO PAGO"/>
@@ -1196,6 +1198,26 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tabla13" displayName="Tabla13" ref="A1:G72" totalsRowShown="0">
+  <autoFilter ref="A1:G72"/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="PLACA"/>
+    <tableColumn id="2" name="FECHAPAGO" dataDxfId="1">
+      <calculatedColumnFormula>DETALLE!H29</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" name="MONTO" dataDxfId="0">
+      <calculatedColumnFormula>DETALLE!I29</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" name="NO PAGO"/>
+    <tableColumn id="5" name="MES"/>
+    <tableColumn id="8" name="OBSERVACIONES"/>
+    <tableColumn id="6" name="ANIO"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Vehiculos" displayName="Vehiculos" ref="A1:Q82" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:Q82">
     <filterColumn colId="0">
@@ -1205,23 +1227,23 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="17">
-    <tableColumn id="35" uniqueName="35" name="Column1" queryTableFieldId="1" dataDxfId="16"/>
-    <tableColumn id="36" uniqueName="36" name="Column2" queryTableFieldId="2" dataDxfId="15"/>
-    <tableColumn id="37" uniqueName="37" name="Column3" queryTableFieldId="3" dataDxfId="14"/>
-    <tableColumn id="38" uniqueName="38" name="Column4" queryTableFieldId="4" dataDxfId="13"/>
-    <tableColumn id="39" uniqueName="39" name="Column5" queryTableFieldId="5" dataDxfId="12"/>
-    <tableColumn id="40" uniqueName="40" name="Column6" queryTableFieldId="6" dataDxfId="11"/>
-    <tableColumn id="41" uniqueName="41" name="Column7" queryTableFieldId="7" dataDxfId="10"/>
-    <tableColumn id="42" uniqueName="42" name="Column8" queryTableFieldId="8" dataDxfId="9"/>
-    <tableColumn id="43" uniqueName="43" name="Column9" queryTableFieldId="9" dataDxfId="8"/>
-    <tableColumn id="44" uniqueName="44" name="Column10" queryTableFieldId="10" dataDxfId="7"/>
-    <tableColumn id="45" uniqueName="45" name="Column11" queryTableFieldId="11" dataDxfId="6"/>
-    <tableColumn id="46" uniqueName="46" name="Column12" queryTableFieldId="12" dataDxfId="5"/>
-    <tableColumn id="47" uniqueName="47" name="Column13" queryTableFieldId="13" dataDxfId="4"/>
-    <tableColumn id="48" uniqueName="48" name="Column14" queryTableFieldId="14" dataDxfId="3"/>
-    <tableColumn id="49" uniqueName="49" name="Column15" queryTableFieldId="15" dataDxfId="2"/>
-    <tableColumn id="50" uniqueName="50" name="Column16" queryTableFieldId="16" dataDxfId="1"/>
-    <tableColumn id="51" uniqueName="51" name="Column17" queryTableFieldId="17" dataDxfId="0"/>
+    <tableColumn id="35" uniqueName="35" name="Column1" queryTableFieldId="1" dataDxfId="18"/>
+    <tableColumn id="36" uniqueName="36" name="Column2" queryTableFieldId="2" dataDxfId="17"/>
+    <tableColumn id="37" uniqueName="37" name="Column3" queryTableFieldId="3" dataDxfId="16"/>
+    <tableColumn id="38" uniqueName="38" name="Column4" queryTableFieldId="4" dataDxfId="15"/>
+    <tableColumn id="39" uniqueName="39" name="Column5" queryTableFieldId="5" dataDxfId="14"/>
+    <tableColumn id="40" uniqueName="40" name="Column6" queryTableFieldId="6" dataDxfId="13"/>
+    <tableColumn id="41" uniqueName="41" name="Column7" queryTableFieldId="7" dataDxfId="12"/>
+    <tableColumn id="42" uniqueName="42" name="Column8" queryTableFieldId="8" dataDxfId="11"/>
+    <tableColumn id="43" uniqueName="43" name="Column9" queryTableFieldId="9" dataDxfId="10"/>
+    <tableColumn id="44" uniqueName="44" name="Column10" queryTableFieldId="10" dataDxfId="9"/>
+    <tableColumn id="45" uniqueName="45" name="Column11" queryTableFieldId="11" dataDxfId="8"/>
+    <tableColumn id="46" uniqueName="46" name="Column12" queryTableFieldId="12" dataDxfId="7"/>
+    <tableColumn id="47" uniqueName="47" name="Column13" queryTableFieldId="13" dataDxfId="6"/>
+    <tableColumn id="48" uniqueName="48" name="Column14" queryTableFieldId="14" dataDxfId="5"/>
+    <tableColumn id="49" uniqueName="49" name="Column15" queryTableFieldId="15" dataDxfId="4"/>
+    <tableColumn id="50" uniqueName="50" name="Column16" queryTableFieldId="16" dataDxfId="3"/>
+    <tableColumn id="51" uniqueName="51" name="Column17" queryTableFieldId="17" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1671,6 +1693,669 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G30"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="12" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="34.5703125" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2" s="41">
+        <v>46030</v>
+      </c>
+      <c r="C2" s="54">
+        <v>150</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G2">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B3" s="41">
+        <v>46048</v>
+      </c>
+      <c r="C3" s="54">
+        <v>60</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0</v>
+      </c>
+      <c r="E3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B4" s="41">
+        <v>46055</v>
+      </c>
+      <c r="C4" s="54">
+        <v>150</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B5" s="41">
+        <v>46025</v>
+      </c>
+      <c r="C5" s="54">
+        <v>160</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B6" s="41">
+        <v>46069</v>
+      </c>
+      <c r="C6" s="54">
+        <v>180</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" t="s">
+        <v>188</v>
+      </c>
+      <c r="G6">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="41">
+        <v>46036</v>
+      </c>
+      <c r="C7" s="54">
+        <v>150</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="41">
+        <v>46065</v>
+      </c>
+      <c r="C8" s="54">
+        <v>55</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" t="s">
+        <v>189</v>
+      </c>
+      <c r="G8">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>162</v>
+      </c>
+      <c r="B9" s="41">
+        <v>46059</v>
+      </c>
+      <c r="C9" s="54">
+        <v>150</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>126</v>
+      </c>
+      <c r="B10" s="41">
+        <v>46086</v>
+      </c>
+      <c r="C10" s="54">
+        <v>150</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
+      <c r="E10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>162</v>
+      </c>
+      <c r="B11" s="41">
+        <v>46099</v>
+      </c>
+      <c r="C11" s="54">
+        <v>150</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
+      <c r="E11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>173</v>
+      </c>
+      <c r="B12" s="41">
+        <v>46066</v>
+      </c>
+      <c r="C12" s="54">
+        <v>60</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0</v>
+      </c>
+      <c r="E12" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>173</v>
+      </c>
+      <c r="B13" s="41">
+        <v>46095</v>
+      </c>
+      <c r="C13" s="54">
+        <v>60</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0</v>
+      </c>
+      <c r="E13" t="s">
+        <v>58</v>
+      </c>
+      <c r="G13">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="41">
+        <v>46001</v>
+      </c>
+      <c r="C14" s="54">
+        <v>0</v>
+      </c>
+      <c r="D14" s="1">
+        <v>150</v>
+      </c>
+      <c r="E14" t="s">
+        <v>83</v>
+      </c>
+      <c r="F14" t="s">
+        <v>71</v>
+      </c>
+      <c r="G14">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="41">
+        <v>46032</v>
+      </c>
+      <c r="C15" s="54">
+        <f>DETALLE!I83</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="1">
+        <v>300</v>
+      </c>
+      <c r="E15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15" t="s">
+        <v>71</v>
+      </c>
+      <c r="G15">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="41">
+        <v>46063</v>
+      </c>
+      <c r="C16" s="54">
+        <f>DETALLE!I84</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="1">
+        <v>450</v>
+      </c>
+      <c r="E16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F16" t="s">
+        <v>71</v>
+      </c>
+      <c r="G16">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="41">
+        <v>42439</v>
+      </c>
+      <c r="C17" s="54">
+        <f>DETALLE!I85</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="1">
+        <v>500</v>
+      </c>
+      <c r="E17" t="s">
+        <v>58</v>
+      </c>
+      <c r="F17" t="s">
+        <v>71</v>
+      </c>
+      <c r="G17">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="B18" s="41">
+        <v>46122</v>
+      </c>
+      <c r="C18" s="54">
+        <f>DETALLE!I86</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="1">
+        <v>650</v>
+      </c>
+      <c r="E18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F18" t="s">
+        <v>190</v>
+      </c>
+      <c r="G18">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>162</v>
+      </c>
+      <c r="B19" s="41">
+        <v>46136</v>
+      </c>
+      <c r="C19" s="54">
+        <v>150</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0</v>
+      </c>
+      <c r="E19" t="s">
+        <v>59</v>
+      </c>
+      <c r="G19">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>162</v>
+      </c>
+      <c r="B20" s="41">
+        <v>46143</v>
+      </c>
+      <c r="C20" s="54">
+        <f>DETALLE!I89</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="1">
+        <v>150</v>
+      </c>
+      <c r="E20" t="s">
+        <v>60</v>
+      </c>
+      <c r="G20">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>162</v>
+      </c>
+      <c r="B21" s="41">
+        <v>46176</v>
+      </c>
+      <c r="C21" s="54">
+        <v>150</v>
+      </c>
+      <c r="D21" s="1">
+        <v>150</v>
+      </c>
+      <c r="E21" t="s">
+        <v>65</v>
+      </c>
+      <c r="G21">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>126</v>
+      </c>
+      <c r="B22" s="41">
+        <v>46118</v>
+      </c>
+      <c r="C22" s="54">
+        <v>150</v>
+      </c>
+      <c r="D22" s="1">
+        <v>0</v>
+      </c>
+      <c r="E22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G22">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23" s="41">
+        <v>46150</v>
+      </c>
+      <c r="C23" s="54">
+        <v>150</v>
+      </c>
+      <c r="D23" s="1">
+        <v>0</v>
+      </c>
+      <c r="E23" t="s">
+        <v>60</v>
+      </c>
+      <c r="G23">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>126</v>
+      </c>
+      <c r="B24" s="41">
+        <v>46023</v>
+      </c>
+      <c r="C24" s="54">
+        <v>150</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0</v>
+      </c>
+      <c r="E24" t="s">
+        <v>65</v>
+      </c>
+      <c r="G24">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>173</v>
+      </c>
+      <c r="B25" s="41">
+        <v>46144</v>
+      </c>
+      <c r="C25" s="54">
+        <v>60</v>
+      </c>
+      <c r="D25" s="1">
+        <v>0</v>
+      </c>
+      <c r="E25" t="s">
+        <v>60</v>
+      </c>
+      <c r="G25">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>173</v>
+      </c>
+      <c r="B26" s="41">
+        <v>46177</v>
+      </c>
+      <c r="C26" s="54">
+        <v>60</v>
+      </c>
+      <c r="D26" s="1">
+        <v>0</v>
+      </c>
+      <c r="E26" t="s">
+        <v>65</v>
+      </c>
+      <c r="G26">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>173</v>
+      </c>
+      <c r="B27" s="41">
+        <v>46207</v>
+      </c>
+      <c r="C27" s="54">
+        <v>60</v>
+      </c>
+      <c r="D27" s="1">
+        <v>0</v>
+      </c>
+      <c r="E27" t="s">
+        <v>66</v>
+      </c>
+      <c r="F27" t="s">
+        <v>191</v>
+      </c>
+      <c r="G27">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="B28" s="41">
+        <v>46144</v>
+      </c>
+      <c r="C28" s="54">
+        <v>300</v>
+      </c>
+      <c r="D28" s="1">
+        <v>400</v>
+      </c>
+      <c r="E28" t="s">
+        <v>60</v>
+      </c>
+      <c r="F28" t="s">
+        <v>192</v>
+      </c>
+      <c r="G28">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="B29" s="41">
+        <v>46183</v>
+      </c>
+      <c r="C29" s="54">
+        <v>0</v>
+      </c>
+      <c r="D29" s="1">
+        <v>600</v>
+      </c>
+      <c r="E29" t="s">
+        <v>65</v>
+      </c>
+      <c r="F29" t="s">
+        <v>193</v>
+      </c>
+      <c r="G29">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="B30" s="41">
+        <v>46213</v>
+      </c>
+      <c r="C30" s="54">
+        <f>DETALLE!I99</f>
+        <v>0</v>
+      </c>
+      <c r="D30" s="1">
+        <v>800</v>
+      </c>
+      <c r="E30" t="s">
+        <v>66</v>
+      </c>
+      <c r="F30" t="s">
+        <v>194</v>
+      </c>
+      <c r="G30">
+        <v>2026</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1705,7 +2390,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1725,7 +2410,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1745,7 +2430,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1765,7 +2450,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1785,7 +2470,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>162</v>
       </c>
@@ -1914,7 +2599,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>126</v>
       </c>
@@ -1937,7 +2622,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -1957,7 +2642,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>162</v>
       </c>
@@ -1997,7 +2682,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>126</v>
       </c>
@@ -2017,7 +2702,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -2037,7 +2722,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>162</v>
       </c>
@@ -2057,7 +2742,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>126</v>
       </c>
@@ -2077,7 +2762,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>173</v>
       </c>
@@ -2097,7 +2782,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -2117,7 +2802,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>162</v>
       </c>
@@ -2140,7 +2825,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>126</v>
       </c>
@@ -2160,7 +2845,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>162</v>
       </c>
@@ -2183,7 +2868,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>12</v>
       </c>
@@ -2226,7 +2911,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>12</v>
       </c>
@@ -2246,7 +2931,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>162</v>
       </c>
@@ -2266,7 +2951,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>126</v>
       </c>
@@ -2286,7 +2971,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>126</v>
       </c>
@@ -2306,7 +2991,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>12</v>
       </c>
@@ -2326,7 +3011,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>162</v>
       </c>
@@ -2389,7 +3074,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>126</v>
       </c>
@@ -2409,7 +3094,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>173</v>
       </c>
@@ -2429,7 +3114,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>12</v>
       </c>
@@ -2449,7 +3134,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>12</v>
       </c>
@@ -2469,7 +3154,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>126</v>
       </c>
@@ -2489,7 +3174,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>162</v>
       </c>
@@ -2509,7 +3194,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>162</v>
       </c>
@@ -2532,7 +3217,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>173</v>
       </c>
@@ -2552,7 +3237,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>126</v>
       </c>
@@ -2572,7 +3257,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>173</v>
       </c>
@@ -2592,7 +3277,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>126</v>
       </c>
@@ -2612,7 +3297,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>162</v>
       </c>
@@ -2632,7 +3317,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>187</v>
       </c>
@@ -2655,7 +3340,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>12</v>
       </c>
@@ -2675,7 +3360,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>12</v>
       </c>
@@ -2698,7 +3383,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>162</v>
       </c>
@@ -2718,7 +3403,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>126</v>
       </c>
@@ -2738,7 +3423,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>162</v>
       </c>
@@ -2758,7 +3443,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>173</v>
       </c>
@@ -2778,7 +3463,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>173</v>
       </c>
@@ -2917,12 +3602,12 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="41"/>
       <c r="B60" s="41"/>
       <c r="C60" s="54"/>
     </row>
-    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>162</v>
       </c>
@@ -2942,7 +3627,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>162</v>
       </c>
@@ -2963,7 +3648,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>162</v>
       </c>
@@ -2983,7 +3668,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>126</v>
       </c>
@@ -3003,7 +3688,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>126</v>
       </c>
@@ -3023,7 +3708,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>126</v>
       </c>
@@ -3043,7 +3728,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>173</v>
       </c>
@@ -3063,7 +3748,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>173</v>
       </c>
@@ -3083,7 +3768,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>173</v>
       </c>
@@ -3184,7 +3869,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:R81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5001,7 +5686,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:J74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6119,7 +6804,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6171,7 +6856,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/CONTROLGARAJE.xlsx
+++ b/CONTROLGARAJE.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="197">
   <si>
     <t>PLACA</t>
   </si>
@@ -649,6 +649,12 @@
   </si>
   <si>
     <t>MAS MOTOCICLETA 150+50+600</t>
+  </si>
+  <si>
+    <t>MAS MOTOCICLETA 50+550</t>
+  </si>
+  <si>
+    <t>MAS MOTOCICLETA 150+50+800</t>
   </si>
 </sst>
 </file>
@@ -1075,13 +1081,6 @@
   <dxfs count="21">
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="d/m/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -1138,6 +1137,13 @@
     <dxf>
       <numFmt numFmtId="19" formatCode="d/m/yyyy"/>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="d/m/yyyy"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1179,7 +1185,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:G30" totalsRowShown="0">
-  <autoFilter ref="A1:G30"/>
+  <autoFilter ref="A1:G30">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="1758GXK"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="7">
     <tableColumn id="1" name="PLACA"/>
     <tableColumn id="2" name="FECHAPAGO" dataDxfId="20">
@@ -1202,10 +1214,10 @@
   <autoFilter ref="A1:G72"/>
   <tableColumns count="7">
     <tableColumn id="1" name="PLACA"/>
-    <tableColumn id="2" name="FECHAPAGO" dataDxfId="1">
+    <tableColumn id="2" name="FECHAPAGO" dataDxfId="18">
       <calculatedColumnFormula>DETALLE!H29</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" name="MONTO" dataDxfId="0">
+    <tableColumn id="3" name="MONTO" dataDxfId="17">
       <calculatedColumnFormula>DETALLE!I29</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" name="NO PAGO"/>
@@ -1227,23 +1239,23 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="17">
-    <tableColumn id="35" uniqueName="35" name="Column1" queryTableFieldId="1" dataDxfId="18"/>
-    <tableColumn id="36" uniqueName="36" name="Column2" queryTableFieldId="2" dataDxfId="17"/>
-    <tableColumn id="37" uniqueName="37" name="Column3" queryTableFieldId="3" dataDxfId="16"/>
-    <tableColumn id="38" uniqueName="38" name="Column4" queryTableFieldId="4" dataDxfId="15"/>
-    <tableColumn id="39" uniqueName="39" name="Column5" queryTableFieldId="5" dataDxfId="14"/>
-    <tableColumn id="40" uniqueName="40" name="Column6" queryTableFieldId="6" dataDxfId="13"/>
-    <tableColumn id="41" uniqueName="41" name="Column7" queryTableFieldId="7" dataDxfId="12"/>
-    <tableColumn id="42" uniqueName="42" name="Column8" queryTableFieldId="8" dataDxfId="11"/>
-    <tableColumn id="43" uniqueName="43" name="Column9" queryTableFieldId="9" dataDxfId="10"/>
-    <tableColumn id="44" uniqueName="44" name="Column10" queryTableFieldId="10" dataDxfId="9"/>
-    <tableColumn id="45" uniqueName="45" name="Column11" queryTableFieldId="11" dataDxfId="8"/>
-    <tableColumn id="46" uniqueName="46" name="Column12" queryTableFieldId="12" dataDxfId="7"/>
-    <tableColumn id="47" uniqueName="47" name="Column13" queryTableFieldId="13" dataDxfId="6"/>
-    <tableColumn id="48" uniqueName="48" name="Column14" queryTableFieldId="14" dataDxfId="5"/>
-    <tableColumn id="49" uniqueName="49" name="Column15" queryTableFieldId="15" dataDxfId="4"/>
-    <tableColumn id="50" uniqueName="50" name="Column16" queryTableFieldId="16" dataDxfId="3"/>
-    <tableColumn id="51" uniqueName="51" name="Column17" queryTableFieldId="17" dataDxfId="2"/>
+    <tableColumn id="35" uniqueName="35" name="Column1" queryTableFieldId="1" dataDxfId="16"/>
+    <tableColumn id="36" uniqueName="36" name="Column2" queryTableFieldId="2" dataDxfId="15"/>
+    <tableColumn id="37" uniqueName="37" name="Column3" queryTableFieldId="3" dataDxfId="14"/>
+    <tableColumn id="38" uniqueName="38" name="Column4" queryTableFieldId="4" dataDxfId="13"/>
+    <tableColumn id="39" uniqueName="39" name="Column5" queryTableFieldId="5" dataDxfId="12"/>
+    <tableColumn id="40" uniqueName="40" name="Column6" queryTableFieldId="6" dataDxfId="11"/>
+    <tableColumn id="41" uniqueName="41" name="Column7" queryTableFieldId="7" dataDxfId="10"/>
+    <tableColumn id="42" uniqueName="42" name="Column8" queryTableFieldId="8" dataDxfId="9"/>
+    <tableColumn id="43" uniqueName="43" name="Column9" queryTableFieldId="9" dataDxfId="8"/>
+    <tableColumn id="44" uniqueName="44" name="Column10" queryTableFieldId="10" dataDxfId="7"/>
+    <tableColumn id="45" uniqueName="45" name="Column11" queryTableFieldId="11" dataDxfId="6"/>
+    <tableColumn id="46" uniqueName="46" name="Column12" queryTableFieldId="12" dataDxfId="5"/>
+    <tableColumn id="47" uniqueName="47" name="Column13" queryTableFieldId="13" dataDxfId="4"/>
+    <tableColumn id="48" uniqueName="48" name="Column14" queryTableFieldId="14" dataDxfId="3"/>
+    <tableColumn id="49" uniqueName="49" name="Column15" queryTableFieldId="15" dataDxfId="2"/>
+    <tableColumn id="50" uniqueName="50" name="Column16" queryTableFieldId="16" dataDxfId="1"/>
+    <tableColumn id="51" uniqueName="51" name="Column17" queryTableFieldId="17" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1700,7 +1712,7 @@
     <col min="3" max="3" width="12" style="1" customWidth="1"/>
     <col min="4" max="4" width="15.5703125" style="1" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="34.5703125" customWidth="1"/>
+    <col min="6" max="6" width="43.85546875" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1727,7 +1739,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>126</v>
       </c>
@@ -1747,7 +1759,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>173</v>
       </c>
@@ -1767,7 +1779,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>126</v>
       </c>
@@ -1787,7 +1799,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>162</v>
       </c>
@@ -1807,7 +1819,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>187</v>
       </c>
@@ -1830,7 +1842,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1850,7 +1862,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1873,7 +1885,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>162</v>
       </c>
@@ -1893,7 +1905,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>126</v>
       </c>
@@ -1913,7 +1925,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>162</v>
       </c>
@@ -1933,7 +1945,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>173</v>
       </c>
@@ -1953,7 +1965,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>173</v>
       </c>
@@ -2092,7 +2104,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>162</v>
       </c>
@@ -2112,7 +2124,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>162</v>
       </c>
@@ -2133,7 +2145,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>162</v>
       </c>
@@ -2153,7 +2165,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>126</v>
       </c>
@@ -2173,7 +2185,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>126</v>
       </c>
@@ -2193,7 +2205,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>126</v>
       </c>
@@ -2213,7 +2225,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>173</v>
       </c>
@@ -2233,7 +2245,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>173</v>
       </c>
@@ -2253,7 +2265,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>173</v>
       </c>
@@ -2287,13 +2299,13 @@
         <v>300</v>
       </c>
       <c r="D28" s="1">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E28" t="s">
         <v>60</v>
       </c>
       <c r="F28" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G28">
         <v>2026</v>
@@ -2310,13 +2322,13 @@
         <v>0</v>
       </c>
       <c r="D29" s="1">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="E29" t="s">
         <v>65</v>
       </c>
       <c r="F29" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G29">
         <v>2026</v>
@@ -2334,13 +2346,13 @@
         <v>0</v>
       </c>
       <c r="D30" s="1">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E30" t="s">
         <v>66</v>
       </c>
       <c r="F30" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G30">
         <v>2026</v>
